--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>19/11 18:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>19/11 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>18/11 03:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>21/11 18:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>19/11 00:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>18/11 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>19/11 01:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>19/11 03:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>200</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>18/11 17:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>19/11 01:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>19/11 03:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>200</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>20/11 18:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>18/11 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>175</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>18/11 16:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>175</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>19/11 15:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>175</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>150</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>19/11 00:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>175</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>19/11 01:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>175</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/11 00:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>175</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>18/11 16:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>20/11 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>140</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45979.07342716603</v>
+        <v>45979.07342716435</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>20/11 16:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>140</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45979.07342716435</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Davos – Am</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Davos – Ambri PiottaSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20/11 19:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45979.13508189785</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HC Presov – Spisska Nova VesExtraliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19/11 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+112%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45979.07342716603</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45979.13508189785</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>20/11 19:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45979.13508189785</v>
+        <v>45979.13508189814</v>
       </c>
     </row>
     <row r="28">
@@ -1625,23 +1623,66 @@
           <t>19/11 17:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>140</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45979.13508189814</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HKM AS Zvo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HKM AS Zvolen – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>18/11 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>1,50%</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>+110%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>45979.13508189785</v>
+      <c r="I29" s="2" t="n">
+        <v>45979.18564773189</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,23 +1666,426 @@
           <t>18/11 17:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>140</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45979.18564773148</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Poprad – S</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Poprad – Slovan BratislavaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>18/11 16:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Presov – S</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Presov – Spisska Nova VesSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19/11 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Rytiri </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HC Rytiri Kladno – HC Kometa BrnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>21/11 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1,50%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>+110%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>45979.18564773189</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Tappara Ta</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tappara Tampere – Sport VaasaFinlande - Finlande Liiga stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20/11 16:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+102%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sparta Prague – ZugEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>18/11 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Djurgården</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Djurgårdens IF – Linköpings HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/11 18:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+98,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zvolen – N</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Zvolen – NitraSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>18/11 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+93,6%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.51re équipe | Laos – Vie</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Laos – VietnamInternational - Qualif. Coupe d'Asie</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/11 12:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+89,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45979.22408071494</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Traktor Tc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Traktor Tcheliabinsk – Metallurg MagnitogorskRussia - KHL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18/11 14:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+88,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45979.22408071494</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -1709,10 +1709,8 @@
           <t>18/11 16:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>175</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>19/11 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>150</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>21/11 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>140</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="33">
@@ -1844,10 +1838,8 @@
           <t>20/11 16:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>150</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1860,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="34">
@@ -1889,10 +1881,8 @@
           <t>18/11 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>140</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1905,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="35">
@@ -1934,10 +1924,8 @@
           <t>20/11 18:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1950,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="36">
@@ -1979,10 +1967,8 @@
           <t>18/11 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>140</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1995,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="37">
@@ -2024,10 +2010,8 @@
           <t>19/11 12:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>75</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2040,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
     <row r="38">
@@ -2069,10 +2053,8 @@
           <t>18/11 14:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>101</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2085,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45979.22408071494</v>
+        <v>45979.22408071759</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,6 +2070,51 @@
         <v>45979.22408071759</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Lugano </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HC Lugano – HC Fribourg-GotteronNational League A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20/11 18:45</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45979.3548312596</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,23 +2096,336 @@
           <t>20/11 18:45</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>150</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45979.35483126157</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – Genève-ServetteSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21/11 18:45</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+221%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Innsbruck </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Innsbruck Die Haie – FTC-TelekomAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21/11 18:15</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+219%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bolzano – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>21/11 18:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KAC Klagen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>KAC Klagenfurt – Spusu Vienna CapitalsICE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21/11 18:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+144%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Biel –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EHC Biel – SCL TigersNational League A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/11 18:45</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+143%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – MM Graz 99ersICE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21/11 18:15</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+140%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45979.39308319462</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – LausanneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21/11 18:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>+131%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>45979.3548312596</v>
+      <c r="I46" s="2" t="n">
+        <v>45979.39308319462</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -2139,10 +2139,8 @@
           <t>21/11 18:45</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>225</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>21/11 18:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>175</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>21/11 18:45</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>150</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="45">
@@ -2364,10 +2354,8 @@
           <t>21/11 18:15</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2380,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
     <row r="46">
@@ -2409,10 +2397,8 @@
           <t>21/11 18:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>140</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2425,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45979.39308319462</v>
+        <v>45979.39308319445</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,51 @@
         <v>45979.39308319445</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.51re équipe | Népal – Ma</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Népal – MalaisieInternational - Qualif. Coupe d'Asie</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>18/11 13:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>95.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+126%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45979.53278046066</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -2440,10 +2440,8 @@
           <t>18/11 13:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>95</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45979.53278046066</v>
+        <v>45979.53278046296</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,186 @@
         <v>45979.53278046296</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Washington</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Washington Capitals – Edmonton OilersNHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/11 00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45979.64318366721</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Minnesota </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Minnesota Wild – Carolina HurricanesNHL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20/11 02:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+161%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45979.64318366721</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – Calgary FlamesNHL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20/11 00:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45979.64318366721</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Frölunda HC – GrenobleLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>18/11 18:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+147%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45979.64318366721</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -2483,10 +2483,8 @@
           <t>20/11 00:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>200</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45979.64318366721</v>
+        <v>45979.64318366898</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>20/11 02:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45979.64318366721</v>
+        <v>45979.64318366898</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>20/11 00:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>200</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45979.64318366721</v>
+        <v>45979.64318366898</v>
       </c>
     </row>
     <row r="51">
@@ -2618,10 +2612,8 @@
           <t>18/11 18:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>175</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2634,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45979.64318366721</v>
+        <v>45979.64318366898</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,51 @@
         <v>45979.64318366898</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | JYP Jyväsk</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JYP Jyväskylä – LukkoFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21/11 16:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+132%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45979.77351558887</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>21/11 16:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>175</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45979.77351558887</v>
+        <v>45979.77351559028</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dresdner E</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dresdner Eislowen – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19/11 15:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45979.80464305589</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>19/11 15:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>150</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,277 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45979.80464305589</v>
+        <v>45979.80464305556</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Grizzlys W</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Grizzlys Wolfsburg – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>21/11 18:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+186%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45979.93244448709</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Pr</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nitra – PresovSlovaquie - Slovaquie Extraliga A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/11 17:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+185%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45979.93244448709</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cologne Haie – AugsbourgDEL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>21/11 18:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+183%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45979.93244448709</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liptovsky </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas – Slovan BratislavaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21/11 17:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45979.93244448709</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>21/11 16:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45979.93244448709</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21/11 18:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+145%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45979.93244448709</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-11-18.xlsx
+++ b/data/valuebets_database_2025-11-18.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>21/11 18:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45979.93244448709</v>
+        <v>45979.93244449074</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>21/11 17:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>200</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45979.93244448709</v>
+        <v>45979.93244449074</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>21/11 18:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>200</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45979.93244448709</v>
+        <v>45979.93244449074</v>
       </c>
     </row>
     <row r="57">
@@ -2876,10 +2870,8 @@
           <t>21/11 17:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>200</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2892,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45979.93244448709</v>
+        <v>45979.93244449074</v>
       </c>
     </row>
     <row r="58">
@@ -2921,10 +2913,8 @@
           <t>21/11 16:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>175</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2937,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45979.93244448709</v>
+        <v>45979.93244449074</v>
       </c>
     </row>
     <row r="59">
@@ -2966,23 +2956,111 @@
           <t>21/11 18:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>175</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+145%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45979.93244449074</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kölner Hai</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Kölner Haie – Augsburger PantherAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>21/11 18:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+174%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45979.97254175419</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – MunichAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>21/11 18:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1,40%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>+145%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>45979.93244448709</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45979.97254175419</v>
       </c>
     </row>
   </sheetData>
